--- a/results/greedy/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03913091594586149</v>
+        <v>0.03913754201494157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03899466700386256</v>
+        <v>0.03829970897641033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02821125002810732</v>
+        <v>0.02766366698779166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0213467080029659</v>
+        <v>0.02113270800327882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02681274997303262</v>
+        <v>0.02632962499046698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03795083297882229</v>
+        <v>0.03757683298317716</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03959875000873581</v>
+        <v>0.03963137499522418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092770802322775</v>
+        <v>0.03092979197390378</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0319684169953689</v>
+        <v>0.03190325002651662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03115537500707433</v>
+        <v>0.03106274997116998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03644604195142165</v>
+        <v>0.03668324998579919</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02597237500594929</v>
+        <v>0.02609354199375957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03836870798841119</v>
+        <v>0.03776712500257418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04556349996710196</v>
+        <v>0.04531754099298269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03189283300889656</v>
+        <v>0.03125366702442989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.039902041957248</v>
+        <v>0.04052233404945582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03432783298194408</v>
+        <v>0.03423904103692621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03183341596741229</v>
+        <v>0.03219883400015533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03008612501434982</v>
+        <v>0.02989920799154788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03466154198395088</v>
+        <v>0.03382954199332744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02763845899607986</v>
+        <v>0.02672562503721565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02385933400364593</v>
+        <v>0.02287854201858863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03474370797630399</v>
+        <v>0.03430083399871364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02430537500185892</v>
+        <v>0.02450083399889991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03470479202223942</v>
+        <v>0.03403312497539446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03931699995882809</v>
+        <v>0.03804429102456197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03601762495236471</v>
+        <v>0.03535862499848008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04154645896051079</v>
+        <v>0.04020341602154076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03457974997581914</v>
+        <v>0.03380329202627763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02618954103672877</v>
+        <v>0.02573491696966812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03964770800666884</v>
+        <v>0.03953270800411701</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04403962503420189</v>
+        <v>0.04324616701342165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03862270800163969</v>
+        <v>0.03754516702610999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03312666597776115</v>
+        <v>0.03204649995313957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03304666699841619</v>
+        <v>0.03308841702528298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04322712501743808</v>
+        <v>0.04262779100099578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02817729098023847</v>
+        <v>0.02742812497308478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998891699826345</v>
+        <v>0.02932620898354799</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03225808398565277</v>
+        <v>0.03101245901780203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0294477500137873</v>
+        <v>0.02908012497937307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03786233300343156</v>
+        <v>0.03739854198647663</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03480466594919562</v>
+        <v>0.0341021660133265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04305116599425673</v>
+        <v>0.04193341598147526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03033445798791945</v>
+        <v>0.0298945420072414</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523604099405929</v>
+        <v>0.02481929102214053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02612466597929597</v>
+        <v>0.02532275003613904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03247770899906754</v>
+        <v>0.03222229098901153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0325719999964349</v>
+        <v>0.03162679204251617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02951799996662885</v>
+        <v>0.02896945900283754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0368862499599345</v>
+        <v>0.03610800002934411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03104641597019508</v>
+        <v>0.03068650001659989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04166137502761558</v>
+        <v>0.04071804200066254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0382187920040451</v>
+        <v>0.03750550001859665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03346612502355129</v>
+        <v>0.03292470797896385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02743654197547585</v>
+        <v>0.02704187500057742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03163108299486339</v>
+        <v>0.03104587498819456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0339713339926675</v>
+        <v>0.03441024996573105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03082883398747072</v>
+        <v>0.03069437498925254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03896825003903359</v>
+        <v>0.0382320000207983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03718679200392216</v>
+        <v>0.03653316700365394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627641602884978</v>
+        <v>0.02548075001686811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02378308394690976</v>
+        <v>0.02337462495779619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03579591697780415</v>
+        <v>0.03453416598495096</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03536837501451373</v>
+        <v>0.0349068749928847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03780479199485853</v>
+        <v>0.03741333301877603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03545920795295388</v>
+        <v>0.03500145900761709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03483849996700883</v>
+        <v>0.03431216697208583</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03493470803368837</v>
+        <v>0.03529895801329985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02853441599290818</v>
+        <v>0.02848445903509855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02943758299807087</v>
+        <v>0.0289857080206275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02924029104178771</v>
+        <v>0.02876058302354068</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298404159839265</v>
+        <v>0.02944966702489182</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0363353340071626</v>
+        <v>0.03524141601519659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092937497422099</v>
+        <v>0.03059320797910914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04035141703207046</v>
+        <v>0.04003083298448473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03217954200226814</v>
+        <v>0.03131674998439848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03632420900976285</v>
+        <v>0.03511408303165808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03678075002972037</v>
+        <v>0.03627791604958475</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02912274998379871</v>
+        <v>0.02909954101778567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03098737500840798</v>
+        <v>0.03028829203685746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03076279204105958</v>
+        <v>0.03057033300865442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02617287501925603</v>
+        <v>0.02522525005042553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03754895797464997</v>
+        <v>0.036670041969046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03094408300239593</v>
+        <v>0.03048162499908358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03004154103109613</v>
+        <v>0.0293622090248391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02967383299255744</v>
+        <v>0.02920016698772088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03070462500909343</v>
+        <v>0.03027116699377075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02962429204490036</v>
+        <v>0.02976420801132917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03015691699692979</v>
+        <v>0.02971791697200388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03404800000134856</v>
+        <v>0.03522291599074379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0325430830125697</v>
+        <v>0.03172937501221895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0347346659982577</v>
+        <v>0.03434216597815976</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03153841703897342</v>
+        <v>0.03092774999095127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02870979096041992</v>
+        <v>0.02852487500058487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03082041599554941</v>
+        <v>0.03072254196740687</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293903750134632</v>
+        <v>0.02890720800496638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04523616703227162</v>
+        <v>0.04456420801579952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03802112501580268</v>
+        <v>0.03679566696519032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0442187919979915</v>
+        <v>0.04320487502263859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03702925000106916</v>
+        <v>0.0365390419610776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03913754201494157</v>
+        <v>0.03884370904415846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03829970897641033</v>
+        <v>0.05805758299538866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02766366698779166</v>
+        <v>0.02765616704709828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02113270800327882</v>
+        <v>0.02084354200633243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02632962499046698</v>
+        <v>0.02561233297456056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03757683298317716</v>
+        <v>0.03604766697390005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03963137499522418</v>
+        <v>0.03841400000965223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092979197390378</v>
+        <v>0.03011587500805035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03190325002651662</v>
+        <v>0.03090224997140467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03106274997116998</v>
+        <v>0.02998366701649502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03668324998579919</v>
+        <v>0.03535312501480803</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02609354199375957</v>
+        <v>0.02565775002585724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03776712500257418</v>
+        <v>0.03783916594693437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04531754099298269</v>
+        <v>0.04466429201420397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03125366702442989</v>
+        <v>0.03084929101169109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04052233404945582</v>
+        <v>0.03898445796221495</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03423904103692621</v>
+        <v>0.03320599999278784</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03219883400015533</v>
+        <v>0.03109845798462629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02989920799154788</v>
+        <v>0.02950708399293944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03382954199332744</v>
+        <v>0.03370545897632837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02672562503721565</v>
+        <v>0.02708408399485052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02287854201858863</v>
+        <v>0.02309983398299664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03430083399871364</v>
+        <v>0.03396824997616932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450083399889991</v>
+        <v>0.02371679100906476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03403312497539446</v>
+        <v>0.03381716698640957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03804429102456197</v>
+        <v>0.03810187504859641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03535862499848008</v>
+        <v>0.03521100000943989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04020341602154076</v>
+        <v>0.04016199999023229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03380329202627763</v>
+        <v>0.03387245797784999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02573491696966812</v>
+        <v>0.0251637080218643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03953270800411701</v>
+        <v>0.03884587500942871</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04324616701342165</v>
+        <v>0.04293183301342651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03754516702610999</v>
+        <v>0.03778499999316409</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03204649995313957</v>
+        <v>0.0324668749817647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03308841702528298</v>
+        <v>0.0321703749941662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04262779100099578</v>
+        <v>0.04235599999083206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02742812497308478</v>
+        <v>0.02718012500554323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932620898354799</v>
+        <v>0.02947433298686519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03101245901780203</v>
+        <v>0.03143754199845716</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02908012497937307</v>
+        <v>0.02826333302073181</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739854198647663</v>
+        <v>0.03729029098758474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0341021660133265</v>
+        <v>0.03373212501173839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04193341598147526</v>
+        <v>0.04168049996951595</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298945420072414</v>
+        <v>0.02936362498439848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02481929102214053</v>
+        <v>0.02430320798885077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02532275003613904</v>
+        <v>0.02523804199881852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03222229098901153</v>
+        <v>0.03154079196974635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03162679204251617</v>
+        <v>0.03162745904410258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02896945900283754</v>
+        <v>0.02888641704339534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03610800002934411</v>
+        <v>0.03612983296625316</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03068650001659989</v>
+        <v>0.03055812499951571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04071804200066254</v>
+        <v>0.04085420799674466</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03750550001859665</v>
+        <v>0.03728191694244742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03292470797896385</v>
+        <v>0.0325272079790011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02704187500057742</v>
+        <v>0.02678216702770442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03104587498819456</v>
+        <v>0.03092033299617469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03441024996573105</v>
+        <v>0.03338349994737655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03069437498925254</v>
+        <v>0.03054708294803277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0382320000207983</v>
+        <v>0.03754504199605435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03653316700365394</v>
+        <v>0.03642629098612815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02548075001686811</v>
+        <v>0.02529908297583461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337462495779619</v>
+        <v>0.02316354104550555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03453416598495096</v>
+        <v>0.03485216700937599</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0349068749928847</v>
+        <v>0.03453349997289479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03741333301877603</v>
+        <v>0.03719166596420109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03500145900761709</v>
+        <v>0.03466754104010761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03431216697208583</v>
+        <v>0.03394649998517707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03529895801329985</v>
+        <v>0.03379050001967698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02848445903509855</v>
+        <v>0.0281287080142647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0289857080206275</v>
+        <v>0.02885654201963916</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02876058302354068</v>
+        <v>0.02871058299206197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02944966702489182</v>
+        <v>0.02918787498492748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03524141601519659</v>
+        <v>0.03536445798818022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03059320797910914</v>
+        <v>0.03016033297171816</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04003083298448473</v>
+        <v>0.03985999996075407</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03131674998439848</v>
+        <v>0.03108599997358397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03511408303165808</v>
+        <v>0.0350414999993518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03627791604958475</v>
+        <v>0.03621670900611207</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02909954101778567</v>
+        <v>0.02827045798767358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028829203685746</v>
+        <v>0.03039387497119606</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03057033300865442</v>
+        <v>0.0300556659931317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522525005042553</v>
+        <v>0.02552295796340331</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.036670041969046</v>
+        <v>0.03629208402708173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03048162499908358</v>
+        <v>0.03013304196065292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293622090248391</v>
+        <v>0.02948658401146531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02920016698772088</v>
+        <v>0.02872170804766938</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03027116699377075</v>
+        <v>0.03015274996869266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02976420801132917</v>
+        <v>0.02947929204674438</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02971791697200388</v>
+        <v>0.02970812498824671</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03522291599074379</v>
+        <v>0.03381320799235255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03172937501221895</v>
+        <v>0.03177554201101884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03434216597815976</v>
+        <v>0.03388504200847819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092774999095127</v>
+        <v>0.03079741704277694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02852487500058487</v>
+        <v>0.02797183400252834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072254196740687</v>
+        <v>0.03037487500114366</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02890720800496638</v>
+        <v>0.02886816702084616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04456420801579952</v>
+        <v>0.04441916599171236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03679566696519032</v>
+        <v>0.03731262497603893</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04320487502263859</v>
+        <v>0.04324333398835734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0365390419610776</v>
+        <v>0.03592408302938566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
